--- a/tables/TableS2.xlsx
+++ b/tables/TableS2.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TableS2_gtex_baseline_results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI80"/>
+  <dimension ref="A1:AI74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -964,15 +965,6 @@
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
         <v>4.5645</v>
       </c>
@@ -1030,15 +1022,6 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
         <v>-1.4912</v>
       </c>
@@ -1150,15 +1133,6 @@
       <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
         <v>-0.06950000000000001</v>
       </c>
@@ -1354,15 +1328,6 @@
       <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
         <v>3.3783</v>
       </c>
@@ -1780,15 +1745,6 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
         <v>-0.8005</v>
       </c>
@@ -1873,15 +1829,6 @@
       <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
         <v>4.7399</v>
       </c>
@@ -1939,15 +1886,6 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
         <v>1.1868</v>
       </c>
@@ -2725,15 +2663,6 @@
       <c r="K22" t="n">
         <v>2</v>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="n">
         <v>-0.4169</v>
       </c>
@@ -3346,15 +3275,6 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="L28" t="n">
         <v>3.6939</v>
       </c>
@@ -3910,15 +3830,6 @@
       <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="n">
         <v>2.0696</v>
       </c>
@@ -4198,15 +4109,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
         <v>-6.9307</v>
       </c>
@@ -4291,15 +4193,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
         <v>4.4436</v>
       </c>
@@ -4384,15 +4277,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
       <c r="L38" t="n">
         <v>-0.008</v>
       </c>
@@ -4477,15 +4361,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
       <c r="L39" t="n">
         <v>3.4332</v>
       </c>
@@ -4597,15 +4472,6 @@
       <c r="K40" t="n">
         <v>2</v>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="n">
         <v>1.2981</v>
       </c>
@@ -4663,15 +4529,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
       <c r="L41" t="n">
         <v>-2.8117</v>
       </c>
@@ -4756,15 +4613,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
       <c r="L42" t="n">
         <v>0.5645</v>
       </c>
@@ -4960,15 +4808,6 @@
           <t>NonCandidate</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
       <c r="L44" t="n">
         <v>0.1573</v>
       </c>
@@ -5378,7 +5217,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RPL13</t>
+          <t>RPL14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5387,109 +5226,109 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-3.1546</v>
+        <v>-2.4388</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0016069663486672</v>
+        <v>0.0147378328520298</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0.0592</v>
+        <v>-0.9844000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9527628722585464</v>
+        <v>0.3249067549077422</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4133</v>
+        <v>-2.0941</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6793813895697818</v>
+        <v>0.0362509478572145</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>-3.1546</v>
+        <v>0.8148</v>
       </c>
       <c r="M48" t="n">
-        <v>0.0016069663486672</v>
+        <v>0.4152054097184707</v>
       </c>
       <c r="N48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>0.0592</v>
+        <v>-0.4695</v>
       </c>
       <c r="P48" t="n">
-        <v>0.9527628722585464</v>
+        <v>0.6386848414613935</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4133</v>
+        <v>-1.3889</v>
       </c>
       <c r="S48" t="n">
-        <v>0.6793813895697817</v>
+        <v>0.1648771724671104</v>
       </c>
       <c r="T48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>-4.4539</v>
+        <v>-1.0142</v>
       </c>
       <c r="V48" t="n">
-        <v>8.432553123538423e-06</v>
+        <v>0.3105084042314713</v>
       </c>
       <c r="W48" t="n">
-        <v>2.775715403164731e-05</v>
+        <v>0.3832838114732224</v>
       </c>
       <c r="X48" t="n">
-        <v>0.08359999999999999</v>
+        <v>-1.0054</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.9333880401890632</v>
+        <v>0.3146914177887411</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.9702323049333684</v>
+        <v>0.4439396786662598</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.5835</v>
+        <v>-2.4301</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.5595382895763892</v>
+        <v>0.0150944067573648</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.7098898052579218</v>
+        <v>0.0313804772061006</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.0016069663486672</v>
+        <v>0.0307653867246576</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.0038469800468094</v>
+        <v>0.0540103455832879</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.9527628722585464</v>
+        <v>0.4863930532678428</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.9775099598496776</v>
+        <v>0.5821977455781755</v>
       </c>
       <c r="AH48" t="n">
-        <v>0.6793813895697818</v>
+        <v>0.0622565340243432</v>
       </c>
       <c r="AI48" t="n">
-        <v>0.7352209558357913</v>
+        <v>0.1046439614451726</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RPL14</t>
+          <t>RPL27A</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5498,109 +5337,109 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2.4388</v>
+        <v>2.4653</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0147378328520298</v>
+        <v>0.0136900793718986</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.669</v>
       </c>
       <c r="G49" t="n">
-        <v>0.3249067549077422</v>
+        <v>0.5034787163819752</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.0941</v>
+        <v>-2.3643</v>
       </c>
       <c r="J49" t="n">
-        <v>0.0362509478572145</v>
+        <v>0.0180653567112382</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>0.8148</v>
+        <v>0.4733</v>
       </c>
       <c r="M49" t="n">
-        <v>0.4152054097184707</v>
+        <v>0.6359972435860786</v>
       </c>
       <c r="N49" t="n">
         <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.4695</v>
+        <v>0.8632</v>
       </c>
       <c r="P49" t="n">
-        <v>0.6386848414613935</v>
+        <v>0.3880020771093462</v>
       </c>
       <c r="Q49" t="n">
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.3889</v>
+        <v>-0.9429</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1648771724671104</v>
+        <v>0.3457135244550097</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>-1.0142</v>
+        <v>1.9935</v>
       </c>
       <c r="V49" t="n">
-        <v>0.3105084042314713</v>
+        <v>0.0462094663441263</v>
       </c>
       <c r="W49" t="n">
-        <v>0.3832838114732224</v>
+        <v>0.07935973567795609</v>
       </c>
       <c r="X49" t="n">
-        <v>-1.0054</v>
+        <v>0.1994</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.3146914177887411</v>
+        <v>0.8419580534406685</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.4439396786662598</v>
+        <v>0.8868624829575041</v>
       </c>
       <c r="AA49" t="n">
-        <v>-2.4301</v>
+        <v>-2.2769</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.0150944067573648</v>
+        <v>0.0227932211097699</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.0313804772061006</v>
+        <v>0.0439186455529714</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.0307653867246576</v>
+        <v>0.029639068707459</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.0540103455832879</v>
+        <v>0.0532156006338468</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.4863930532678428</v>
+        <v>0.4405448623216383</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.5821977455781755</v>
+        <v>0.5437975644282723</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.0622565340243432</v>
+        <v>0.0369661677699333</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.1046439614451726</v>
+        <v>0.0679145872982496</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RPL17</t>
+          <t>RPL7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5609,109 +5448,82 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5.8067</v>
+        <v>2.1763</v>
       </c>
       <c r="D50" t="n">
-        <v>6.372589280313798e-09</v>
+        <v>0.0295306201222445</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.27</v>
+        <v>0.6122</v>
       </c>
       <c r="G50" t="n">
-        <v>3.610490383164236e-10</v>
+        <v>0.5404088271853722</v>
       </c>
       <c r="H50" t="n">
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3135</v>
+        <v>-1.0026</v>
       </c>
       <c r="J50" t="n">
-        <v>0.7539310921589095</v>
+        <v>0.316059582323263</v>
       </c>
       <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="n">
-        <v>-2.9221</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.0034772624255721</v>
-      </c>
-      <c r="N50" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" t="n">
-        <v>6.8622</v>
-      </c>
-      <c r="P50" t="n">
-        <v>6.77870726115543e-12</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1</v>
-      </c>
-      <c r="R50" t="n">
-        <v>-1.2639</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.206250684079983</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
       <c r="U50" t="n">
-        <v>-6.0447</v>
+        <v>2.1763</v>
       </c>
       <c r="V50" t="n">
-        <v>1.496890033972634e-09</v>
+        <v>0.0295328355511147</v>
       </c>
       <c r="W50" t="n">
-        <v>7.390894542739883e-09</v>
+        <v>0.0555498573461443</v>
       </c>
       <c r="X50" t="n">
-        <v>0.952</v>
+        <v>0.6122</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3411029769091757</v>
+        <v>0.5404054415885091</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.4702260866226311</v>
+        <v>0.6468489376589731</v>
       </c>
       <c r="AA50" t="n">
-        <v>-0.7351</v>
+        <v>-1.0026</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.4623049255583813</v>
+        <v>0.3160538958156703</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.6190184596459682</v>
+        <v>0.4657660339270856</v>
       </c>
       <c r="AD50" t="n">
-        <v>1.352406753252211e-08</v>
+        <v>0.0295306201222444</v>
       </c>
       <c r="AE50" t="n">
-        <v>6.284713735701451e-08</v>
+        <v>0.0532156006338468</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.260813675685313e-11</v>
+        <v>0.5404088271853722</v>
       </c>
       <c r="AG50" t="n">
-        <v>5.533571132174429e-11</v>
+        <v>0.6231592222444213</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.432415784995838</v>
+        <v>0.316059582323263</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.5337632346042375</v>
+        <v>0.4231984237887758</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RPL27A</t>
+          <t>RPN1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5720,109 +5532,109 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.4653</v>
+        <v>-0.3721</v>
       </c>
       <c r="D51" t="n">
-        <v>0.0136900793718986</v>
+        <v>0.7098098750153219</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.669</v>
+        <v>0.3423</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5034787163819752</v>
+        <v>0.7321047767076105</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.3643</v>
+        <v>2.9578</v>
       </c>
       <c r="J51" t="n">
-        <v>0.0180653567112382</v>
+        <v>0.0030985177068977</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4733</v>
+        <v>-2.7063</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6359972435860786</v>
+        <v>0.0068045970099581</v>
       </c>
       <c r="N51" t="n">
         <v>2</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8632</v>
+        <v>1.471</v>
       </c>
       <c r="P51" t="n">
-        <v>0.3880020771093462</v>
+        <v>0.1412825114330901</v>
       </c>
       <c r="Q51" t="n">
         <v>2</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.9429</v>
+        <v>2.7169</v>
       </c>
       <c r="S51" t="n">
-        <v>0.3457135244550097</v>
+        <v>0.0065899958623469</v>
       </c>
       <c r="T51" t="n">
         <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>1.9935</v>
+        <v>-2.2681</v>
       </c>
       <c r="V51" t="n">
-        <v>0.0462094663441263</v>
+        <v>0.0233255101671555</v>
       </c>
       <c r="W51" t="n">
-        <v>0.07935973567795609</v>
+        <v>0.0472491103385971</v>
       </c>
       <c r="X51" t="n">
-        <v>0.1994</v>
+        <v>1.326</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.8419580534406685</v>
+        <v>0.1848508425316802</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.8868624829575041</v>
+        <v>0.2863375796078969</v>
       </c>
       <c r="AA51" t="n">
-        <v>-2.2769</v>
+        <v>3.9962</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.0227932211097699</v>
+        <v>6.437128716339633e-05</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.0439186455529714</v>
+        <v>0.0002034132674363</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.029639068707459</v>
+        <v>0.0130555021639104</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.0532156006338468</v>
+        <v>0.0264457607935622</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.4405448623216383</v>
+        <v>0.3075074886155875</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.5437975644282723</v>
+        <v>0.4117473152649392</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.0369661677699333</v>
+        <v>0.0043045207354356</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.0679145872982496</v>
+        <v>0.0106267855656067</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RPL7</t>
+          <t>RPS3A</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5831,91 +5643,82 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.1763</v>
+        <v>-1.6612</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0295306201222445</v>
+        <v>0.0966762711078278</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6122</v>
+        <v>2.8864</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5404088271853722</v>
+        <v>0.0038973826911825</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.0026</v>
+        <v>-6.2233</v>
       </c>
       <c r="J52" t="n">
-        <v>0.316059582323263</v>
+        <v>4.86956112682392e-10</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+        <v>2</v>
+      </c>
       <c r="U52" t="n">
-        <v>2.1763</v>
+        <v>-1.6612</v>
       </c>
       <c r="V52" t="n">
-        <v>0.0295328355511147</v>
+        <v>0.0966732855891517</v>
       </c>
       <c r="W52" t="n">
-        <v>0.0555498573461443</v>
+        <v>0.1527437912308596</v>
       </c>
       <c r="X52" t="n">
-        <v>0.6122</v>
+        <v>2.8864</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.5404054415885091</v>
+        <v>0.0038967655771822</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.6468489376589731</v>
+        <v>0.009930467116045</v>
       </c>
       <c r="AA52" t="n">
-        <v>-1.0026</v>
+        <v>-6.2233</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.3160538958156703</v>
+        <v>4.86805262688111e-10</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.4657660339270856</v>
+        <v>2.746972553740055e-09</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.0295306201222444</v>
+        <v>0.0966762711078277</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.0532156006338468</v>
+        <v>0.1441023663682716</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.5404088271853722</v>
+        <v>0.0038973826911825</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.6231592222444213</v>
+        <v>0.009330097957679299</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.316059582323263</v>
+        <v>4.869560865650158e-10</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.4231984237887758</v>
+        <v>2.024712149401908e-09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RPL7A</t>
+          <t>RPS8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5924,109 +5727,109 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-0.1196</v>
+        <v>8.515700000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9048136592122616</v>
+        <v>1.656315901691188e-17</v>
       </c>
       <c r="E53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.9765</v>
+        <v>6.8474</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0481030586934501</v>
+        <v>7.518629784142033e-12</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.0204</v>
+        <v>2.7498</v>
       </c>
       <c r="J53" t="n">
-        <v>0.3075374273575147</v>
+        <v>0.0059632688535538</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.1666</v>
+        <v>8.515700000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>0.2433615243691831</v>
+        <v>1.656315901691188e-17</v>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0.7909</v>
+        <v>6.8474</v>
       </c>
       <c r="P53" t="n">
-        <v>0.4290242172085582</v>
+        <v>7.518629784142033e-12</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.5244</v>
+        <v>2.7498</v>
       </c>
       <c r="S53" t="n">
-        <v>0.1274037159610713</v>
+        <v>0.0059632688535538</v>
       </c>
       <c r="T53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>0.7914</v>
+        <v>12.0231</v>
       </c>
       <c r="V53" t="n">
-        <v>0.4287044365654029</v>
+        <v>2.687185033183857e-33</v>
       </c>
       <c r="W53" t="n">
-        <v>0.4908355143285047</v>
+        <v>5.307190440538116e-32</v>
       </c>
       <c r="X53" t="n">
-        <v>-0.7244</v>
+        <v>9.6677</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.4687949561166088</v>
+        <v>4.137107197078264e-22</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.578668773956439</v>
+        <v>2.723595571409857e-21</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.4593</v>
+        <v>3.8824</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.6460479518484885</v>
+        <v>0.000103443076627</v>
       </c>
       <c r="AC53" t="n">
-        <v>0.7188420872680366</v>
+        <v>0.0003026667797607</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.74632252480706</v>
+        <v>9.992007221626409e-16</v>
       </c>
       <c r="AE53" t="n">
-        <v>0.818881659163302</v>
+        <v>1.66644475996236e-14</v>
       </c>
       <c r="AF53" t="n">
-        <v>0.0960108463479608</v>
+        <v>7.518596856215254e-12</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.1516971372297781</v>
+        <v>3.712307197756282e-11</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.1800284631222585</v>
+        <v>0.0059632688535538</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.2796810398242234</v>
+        <v>0.0142757042251742</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RPN1</t>
+          <t>RRBP1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6035,109 +5838,109 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-0.3721</v>
+        <v>1.9256</v>
       </c>
       <c r="D54" t="n">
-        <v>0.7098098750153219</v>
+        <v>0.0541574628437681</v>
       </c>
       <c r="E54" t="n">
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3423</v>
+        <v>-1.5437</v>
       </c>
       <c r="G54" t="n">
-        <v>0.7321047767076105</v>
+        <v>0.1226688257835196</v>
       </c>
       <c r="H54" t="n">
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>2.9578</v>
+        <v>0.9096</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0030985177068977</v>
+        <v>0.3630179687544873</v>
       </c>
       <c r="K54" t="n">
         <v>3</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.7063</v>
+        <v>1.0946</v>
       </c>
       <c r="M54" t="n">
-        <v>0.0068045970099581</v>
+        <v>0.2736816082258236</v>
       </c>
       <c r="N54" t="n">
         <v>2</v>
       </c>
       <c r="O54" t="n">
-        <v>1.471</v>
+        <v>1.3665</v>
       </c>
       <c r="P54" t="n">
-        <v>0.1412825114330901</v>
+        <v>0.1717879354067657</v>
       </c>
       <c r="Q54" t="n">
         <v>2</v>
       </c>
       <c r="R54" t="n">
-        <v>2.7169</v>
+        <v>-0.3309</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0065899958623469</v>
+        <v>0.7407046412918026</v>
       </c>
       <c r="T54" t="n">
         <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>-2.2681</v>
+        <v>2.0983</v>
       </c>
       <c r="V54" t="n">
-        <v>0.0233255101671555</v>
+        <v>0.0358800991763829</v>
       </c>
       <c r="W54" t="n">
-        <v>0.0472491103385971</v>
+        <v>0.0659192519752152</v>
       </c>
       <c r="X54" t="n">
-        <v>1.326</v>
+        <v>-0.0068</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.1848508425316802</v>
+        <v>0.994599669286962</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.2863375796078969</v>
+        <v>0.994599669286962</v>
       </c>
       <c r="AA54" t="n">
-        <v>3.9962</v>
+        <v>0.3581</v>
       </c>
       <c r="AB54" t="n">
-        <v>6.437128716339633e-05</v>
+        <v>0.720276622823373</v>
       </c>
       <c r="AC54" t="n">
-        <v>0.0002034132674363</v>
+        <v>0.779477441137623</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.0130555021639104</v>
+        <v>0.0964636706265226</v>
       </c>
       <c r="AE54" t="n">
-        <v>0.0264457607935622</v>
+        <v>0.1441023663682716</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.3075074886155875</v>
+        <v>0.1448085612610058</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.4117473152649392</v>
+        <v>0.2079977516294448</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.0043045207354356</v>
+        <v>0.5876337670185141</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.0106267855656067</v>
+        <v>0.6797057006862227</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RPS3A</t>
+          <t>UBA52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6146,739 +5949,721 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1.6612</v>
+        <v>0.2743</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0966762711078278</v>
+        <v>0.7838647620049906</v>
       </c>
       <c r="E55" t="n">
         <v>2</v>
       </c>
       <c r="F55" t="n">
-        <v>2.8864</v>
+        <v>0.869</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0038973826911825</v>
+        <v>0.3848318780720781</v>
       </c>
       <c r="H55" t="n">
         <v>2</v>
       </c>
       <c r="I55" t="n">
-        <v>-6.2233</v>
+        <v>-1.9494</v>
       </c>
       <c r="J55" t="n">
-        <v>4.86956112682392e-10</v>
+        <v>0.051243819551629</v>
       </c>
       <c r="K55" t="n">
         <v>2</v>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+      <c r="L55" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.8453890675864304</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.6738717509360882</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>2</v>
+      </c>
+      <c r="R55" t="n">
+        <v>-2.6012</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.009289091309594001</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
       <c r="U55" t="n">
-        <v>-1.6612</v>
+        <v>0.3281</v>
       </c>
       <c r="V55" t="n">
-        <v>0.0966732855891517</v>
+        <v>0.7428572337614729</v>
       </c>
       <c r="W55" t="n">
-        <v>0.1527437912308596</v>
+        <v>0.8039139927007721</v>
       </c>
       <c r="X55" t="n">
-        <v>2.8864</v>
+        <v>0.8923</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.0038967655771822</v>
+        <v>0.3722351642530653</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.009930467116045</v>
+        <v>0.4820750487867568</v>
       </c>
       <c r="AA55" t="n">
-        <v>-6.2233</v>
+        <v>-3.2389</v>
       </c>
       <c r="AB55" t="n">
-        <v>4.86805262688111e-10</v>
+        <v>0.0011997585803006</v>
       </c>
       <c r="AC55" t="n">
-        <v>2.746972553740055e-09</v>
+        <v>0.0030574492852822</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.0966762711078277</v>
+        <v>0.8208928062628882</v>
       </c>
       <c r="AE55" t="n">
-        <v>0.1441023663682716</v>
+        <v>0.8883634478735366</v>
       </c>
       <c r="AF55" t="n">
-        <v>0.0038973826911825</v>
+        <v>0.545254763740345</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.009330097957679299</v>
+        <v>0.6231592222444213</v>
       </c>
       <c r="AH55" t="n">
-        <v>4.869560865650158e-10</v>
+        <v>0.0151340712984584</v>
       </c>
       <c r="AI55" t="n">
-        <v>2.024712149401908e-09</v>
+        <v>0.0332108786827282</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RPS8</t>
+          <t>APPL1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.515700000000001</v>
+        <v>-7.811</v>
       </c>
       <c r="D56" t="n">
-        <v>1.656315901691188e-17</v>
+        <v>5.67410340692271e-15</v>
       </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>6.8474</v>
+        <v>1.3446</v>
       </c>
       <c r="G56" t="n">
-        <v>7.518629784142033e-12</v>
+        <v>0.178748608686351</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>2.7498</v>
+        <v>-10.0079</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0059632688535538</v>
+        <v>1.406599582138242e-23</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="n">
-        <v>8.515700000000001</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.656315901691188e-17</v>
-      </c>
-      <c r="N56" t="n">
-        <v>1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>6.8474</v>
-      </c>
-      <c r="P56" t="n">
-        <v>7.518629784142033e-12</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="n">
-        <v>2.7498</v>
-      </c>
-      <c r="S56" t="n">
-        <v>0.0059632688535538</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
       <c r="U56" t="n">
-        <v>12.0231</v>
+        <v>-7.811</v>
       </c>
       <c r="V56" t="n">
-        <v>2.687185033183857e-33</v>
+        <v>5.673601504971163e-15</v>
       </c>
       <c r="W56" t="n">
-        <v>5.307190440538116e-32</v>
+        <v>4.482145188927219e-14</v>
       </c>
       <c r="X56" t="n">
-        <v>9.6677</v>
+        <v>1.3446</v>
       </c>
       <c r="Y56" t="n">
-        <v>4.137107197078264e-22</v>
+        <v>0.1787544433660084</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.723595571409857e-21</v>
+        <v>0.2824320205182933</v>
       </c>
       <c r="AA56" t="n">
-        <v>3.8824</v>
+        <v>-10.0079</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.000103443076627</v>
+        <v>1.407075338180493e-23</v>
       </c>
       <c r="AC56" t="n">
-        <v>0.0003026667797607</v>
+        <v>1.389486896453237e-22</v>
       </c>
       <c r="AD56" t="n">
+        <v>5.662137425588298e-15</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>4.066444151104323e-14</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0.178748608686351</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0.252163215825388</v>
+      </c>
+      <c r="AH56" t="n">
         <v>9.992007221626409e-16</v>
       </c>
-      <c r="AE56" t="n">
-        <v>1.66644475996236e-14</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>7.518596856215254e-12</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>3.712307197756282e-11</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>0.0059632688535538</v>
-      </c>
       <c r="AI56" t="n">
-        <v>0.0142757042251742</v>
+        <v>1.11096317330824e-14</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RRBP1</t>
+          <t>ARAP1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.9256</v>
+        <v>-2.1893</v>
       </c>
       <c r="D57" t="n">
-        <v>0.0541574628437681</v>
+        <v>0.0285764313249237</v>
       </c>
       <c r="E57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.5437</v>
+        <v>-2.2401</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1226688257835196</v>
+        <v>0.0250820660098416</v>
       </c>
       <c r="H57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I57" t="n">
-        <v>0.9096</v>
+        <v>1.0072</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3630179687544873</v>
+        <v>0.3138422736412377</v>
       </c>
       <c r="K57" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" t="n">
-        <v>1.0946</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0.2736816082258236</v>
-      </c>
-      <c r="N57" t="n">
-        <v>2</v>
-      </c>
-      <c r="O57" t="n">
-        <v>1.3665</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0.1717879354067657</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>2</v>
-      </c>
-      <c r="R57" t="n">
-        <v>-0.3309</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.7407046412918026</v>
-      </c>
-      <c r="T57" t="n">
         <v>2</v>
       </c>
       <c r="U57" t="n">
-        <v>2.0983</v>
+        <v>-2.1893</v>
       </c>
       <c r="V57" t="n">
-        <v>0.0358800991763829</v>
+        <v>0.0285750423661574</v>
       </c>
       <c r="W57" t="n">
-        <v>0.0659192519752152</v>
+        <v>0.0550592279738154</v>
       </c>
       <c r="X57" t="n">
-        <v>-0.0068</v>
+        <v>-2.2401</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.994599669286962</v>
+        <v>0.0250844315458308</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.994599669286962</v>
+        <v>0.0535586511383956</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.3581</v>
+        <v>1.0072</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.720276622823373</v>
+        <v>0.3138386730839759</v>
       </c>
       <c r="AC57" t="n">
-        <v>0.779477441137623</v>
+        <v>0.4657660339270856</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.0964636706265226</v>
+        <v>0.0285764313249237</v>
       </c>
       <c r="AE57" t="n">
-        <v>0.1441023663682716</v>
+        <v>0.0532156006338468</v>
       </c>
       <c r="AF57" t="n">
-        <v>0.1448085612610058</v>
+        <v>0.0250820660098415</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.2079977516294448</v>
+        <v>0.0508072619173714</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.5876337670185141</v>
+        <v>0.3138422736412377</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.6797057006862227</v>
+        <v>0.4231984237887758</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SERPINH1</t>
+          <t>CAMK1D</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-14.5157</v>
+        <v>3.6323</v>
       </c>
       <c r="D58" t="n">
-        <v>9.642305819362207e-48</v>
+        <v>0.0002808956445578</v>
       </c>
       <c r="E58" t="n">
         <v>2</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.8357</v>
+        <v>1.8158</v>
       </c>
       <c r="G58" t="n">
-        <v>3.731835060004353e-71</v>
+        <v>0.0694002600206037</v>
       </c>
       <c r="H58" t="n">
         <v>2</v>
       </c>
       <c r="I58" t="n">
-        <v>-9.304</v>
+        <v>1.9132</v>
       </c>
       <c r="J58" t="n">
-        <v>1.35263556037744e-20</v>
+        <v>0.0557198680582857</v>
       </c>
       <c r="K58" t="n">
         <v>2</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.0797</v>
+        <v>3.9862</v>
       </c>
       <c r="M58" t="n">
-        <v>0.2802873083177302</v>
+        <v>6.712664830009929e-05</v>
       </c>
       <c r="N58" t="n">
         <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.0321</v>
+        <v>2.8468</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3020063661120674</v>
+        <v>0.0044154647442019</v>
       </c>
       <c r="Q58" t="n">
         <v>2</v>
       </c>
       <c r="R58" t="n">
-        <v>0.4332</v>
+        <v>-2.2566</v>
       </c>
       <c r="S58" t="n">
-        <v>0.6648612789190276</v>
+        <v>0.0240354968781957</v>
       </c>
       <c r="T58" t="n">
         <v>2</v>
       </c>
       <c r="U58" t="n">
-        <v>-10.4631</v>
+        <v>5.3926</v>
       </c>
       <c r="V58" t="n">
-        <v>1.276324783291324e-25</v>
+        <v>6.945732676918269e-08</v>
       </c>
       <c r="W58" t="n">
-        <v>1.680494298000243e-24</v>
+        <v>3.227722832214961e-07</v>
       </c>
       <c r="X58" t="n">
-        <v>-12.6363</v>
+        <v>3.3334</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.332235816967606e-36</v>
+        <v>0.0008578532228143</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.503523279149156e-35</v>
+        <v>0.0026065540231666</v>
       </c>
       <c r="AA58" t="n">
-        <v>-5.8663</v>
+        <v>-0.412</v>
       </c>
       <c r="AB58" t="n">
-        <v>4.4555339131255e-09</v>
+        <v>0.6803720208725349</v>
       </c>
       <c r="AC58" t="n">
-        <v>2.070512818452438e-08</v>
+        <v>0.7465193006795869</v>
       </c>
       <c r="AD58" t="n">
-        <v>2.109423746787797e-15</v>
+        <v>0.0001046560677132</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.66644475996236e-14</v>
+        <v>0.0003062159018275</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.109423746787797e-15</v>
+        <v>0.007907617288291501</v>
       </c>
       <c r="AG58" t="n">
-        <v>1.3887039666353e-14</v>
+        <v>0.0178486218792867</v>
       </c>
       <c r="AH58" t="n">
-        <v>2.109423746787797e-15</v>
+        <v>0.0328546405277713</v>
       </c>
       <c r="AI58" t="n">
-        <v>1.11096317330824e-14</v>
+        <v>0.0639912094596449</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TPM4</t>
+          <t>CDKAL1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1.8469</v>
+        <v>-2.0927</v>
       </c>
       <c r="D59" t="n">
-        <v>0.06475703820113229</v>
+        <v>0.0363775144756356</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.2673</v>
+        <v>-1.5653</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2050584380032687</v>
+        <v>0.1175049670460892</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2898</v>
+        <v>-1.5143</v>
       </c>
       <c r="J59" t="n">
-        <v>0.7719713133418309</v>
+        <v>0.1299446868966723</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="L59" t="n">
+        <v>6.6261</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.446535018940334e-11</v>
+      </c>
+      <c r="N59" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>9.1975</v>
+      </c>
+      <c r="P59" t="n">
+        <v>3.663173202964827e-20</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.3392996943147763</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
       <c r="U59" t="n">
-        <v>1.8469</v>
+        <v>3.5548</v>
       </c>
       <c r="V59" t="n">
-        <v>0.0647616347515212</v>
+        <v>0.000378287505112</v>
       </c>
       <c r="W59" t="n">
-        <v>0.1088546626674505</v>
+        <v>0.0009961570967951</v>
       </c>
       <c r="X59" t="n">
-        <v>-1.2673</v>
+        <v>5.8254</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.2050480405342105</v>
+        <v>5.69594973925359e-09</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.3061345443327083</v>
+        <v>2.368315944215966e-08</v>
       </c>
       <c r="AA59" t="n">
-        <v>-0.2898</v>
+        <v>-0.2941</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.7719692478667453</v>
+        <v>0.7687122242793872</v>
       </c>
       <c r="AC59" t="n">
         <v>0.813140941086305</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.06475703820113229</v>
+        <v>6.517697492824935e-11</v>
       </c>
       <c r="AE59" t="n">
-        <v>0.1044042044467235</v>
+        <v>3.4326540128878e-10</v>
       </c>
       <c r="AF59" t="n">
-        <v>0.2050584380032687</v>
+        <v>1.887379141862766e-15</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.2842038000396181</v>
+        <v>1.3887039666353e-14</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.7719713133418309</v>
+        <v>0.1994242852337244</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.8241315372162789</v>
+        <v>0.3029715102589275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>UBA52</t>
+          <t>DUSP8</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.2743</v>
+        <v>-2.0892</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7838647620049906</v>
+        <v>0.0366929545235972</v>
       </c>
       <c r="E60" t="n">
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>0.869</v>
+        <v>-1.1506</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3848318780720781</v>
+        <v>0.2498869481516166</v>
       </c>
       <c r="H60" t="n">
         <v>2</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.9494</v>
+        <v>1.4254</v>
       </c>
       <c r="J60" t="n">
-        <v>0.051243819551629</v>
+        <v>0.1540309916336558</v>
       </c>
       <c r="K60" t="n">
         <v>2</v>
       </c>
       <c r="L60" t="n">
-        <v>0.195</v>
+        <v>6.2101</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8453890675864304</v>
+        <v>5.296314080169554e-10</v>
       </c>
       <c r="N60" t="n">
         <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>0.4208</v>
+        <v>-3.8558</v>
       </c>
       <c r="P60" t="n">
-        <v>0.6738717509360882</v>
+        <v>0.0001153738035338</v>
       </c>
       <c r="Q60" t="n">
         <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>-2.6012</v>
+        <v>2.897</v>
       </c>
       <c r="S60" t="n">
-        <v>0.009289091309594001</v>
+        <v>0.0037671075975908</v>
       </c>
       <c r="T60" t="n">
         <v>2</v>
       </c>
       <c r="U60" t="n">
-        <v>0.3281</v>
+        <v>3.2465</v>
       </c>
       <c r="V60" t="n">
-        <v>0.7428572337614729</v>
+        <v>0.0011682095779781</v>
       </c>
       <c r="W60" t="n">
-        <v>0.8039139927007721</v>
+        <v>0.0027966229290992</v>
       </c>
       <c r="X60" t="n">
-        <v>0.8923</v>
+        <v>-3.6442</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.3722351642530653</v>
+        <v>0.0002682339595988</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.4820750487867568</v>
+        <v>0.0008476193123323</v>
       </c>
       <c r="AA60" t="n">
-        <v>-3.2389</v>
+        <v>3.1112</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.0011997585803006</v>
+        <v>0.0018634488452516</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.0030574492852822</v>
+        <v>0.0046003893367149</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.8208928062628882</v>
+        <v>1.001577210058002e-09</v>
       </c>
       <c r="AE60" t="n">
-        <v>0.8883634478735366</v>
+        <v>4.945287474661386e-09</v>
       </c>
       <c r="AF60" t="n">
-        <v>0.545254763740345</v>
+        <v>0.0002181109791081</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.6231592222444213</v>
+        <v>0.0006153845481979</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.0151340712984584</v>
+        <v>0.0069829855726626</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.0332108786827282</v>
+        <v>0.0162251723600102</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VAT1</t>
+          <t>FTO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NonCandidate</t>
+          <t>T2DM_Control</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-0.5921</v>
+        <v>-0.0621</v>
       </c>
       <c r="D61" t="n">
-        <v>0.553779461542804</v>
+        <v>0.9504993091358028</v>
       </c>
       <c r="E61" t="n">
         <v>1</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.3519</v>
+        <v>4.7555</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7249210022508934</v>
+        <v>1.979164533662419e-06</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.9028</v>
+        <v>-12.8992</v>
       </c>
       <c r="J61" t="n">
-        <v>0.0570685207907404</v>
+        <v>4.547462963785542e-38</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.6357</v>
+        <v>9.3398</v>
       </c>
       <c r="M61" t="n">
-        <v>0.5249684552697977</v>
+        <v>9.65465651174031e-21</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.3804</v>
+        <v>19.6962</v>
       </c>
       <c r="P61" t="n">
-        <v>0.7036852057267966</v>
+        <v>2.326425266493951e-86</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.7857</v>
+        <v>-2.0606</v>
       </c>
       <c r="S61" t="n">
-        <v>0.0741438294763882</v>
+        <v>0.0393430825266283</v>
       </c>
       <c r="T61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>-0.8685</v>
+        <v>6.9317</v>
       </c>
       <c r="V61" t="n">
-        <v>0.385108620132337</v>
+        <v>4.157083090136175e-12</v>
       </c>
       <c r="W61" t="n">
-        <v>0.4568747683179193</v>
+        <v>2.756858168127347e-11</v>
       </c>
       <c r="X61" t="n">
-        <v>-0.5181</v>
+        <v>17.8688</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.6043770920406848</v>
+        <v>2.063120156296528e-71</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.6919679749451318</v>
+        <v>4.074662308685641e-70</v>
       </c>
       <c r="AA61" t="n">
-        <v>-2.5991</v>
+        <v>-10.12</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.009347203311034599</v>
+        <v>4.504328349173042e-24</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.0199575422046415</v>
+        <v>5.083456279781005e-23</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.5386246360694088</v>
+        <v>1.887379141862766e-15</v>
       </c>
       <c r="AE61" t="n">
-        <v>0.6350947201415418</v>
+        <v>1.66644475996236e-14</v>
       </c>
       <c r="AF61" t="n">
-        <v>0.7139735292400499</v>
+        <v>1.887379141862766e-15</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.7726562850679992</v>
+        <v>1.3887039666353e-14</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.064997726001341</v>
+        <v>2.109423746787797e-15</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.1069754240438737</v>
+        <v>1.11096317330824e-14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>APPL1</t>
+          <t>GCK</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6887,91 +6672,82 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-7.811</v>
+        <v>2.3971</v>
       </c>
       <c r="D62" t="n">
-        <v>5.67410340692271e-15</v>
+        <v>0.0165264569403382</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>1.3446</v>
+        <v>-2.9019</v>
       </c>
       <c r="G62" t="n">
-        <v>0.178748608686351</v>
+        <v>0.0037092938486616</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>-10.0079</v>
+        <v>-0.0864</v>
       </c>
       <c r="J62" t="n">
-        <v>1.406599582138242e-23</v>
+        <v>0.931174569989936</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+        <v>3</v>
+      </c>
       <c r="U62" t="n">
-        <v>-7.811</v>
+        <v>2.3971</v>
       </c>
       <c r="V62" t="n">
-        <v>5.673601504971163e-15</v>
+        <v>0.0165254130035821</v>
       </c>
       <c r="W62" t="n">
-        <v>4.482145188927219e-14</v>
+        <v>0.0352839899265673</v>
       </c>
       <c r="X62" t="n">
-        <v>1.3446</v>
+        <v>-2.9019</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.1787544433660084</v>
+        <v>0.0037090691938899</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.2824320205182933</v>
+        <v>0.0097672155439103</v>
       </c>
       <c r="AA62" t="n">
-        <v>-10.0079</v>
+        <v>-0.0864</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.407075338180493e-23</v>
+        <v>0.9311484469318309</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.389486896453237e-22</v>
+        <v>0.9430862475335208</v>
       </c>
       <c r="AD62" t="n">
-        <v>5.662137425588298e-15</v>
+        <v>0.0165264569403382</v>
       </c>
       <c r="AE62" t="n">
-        <v>4.066444151104323e-14</v>
+        <v>0.0326397524571679</v>
       </c>
       <c r="AF62" t="n">
-        <v>0.178748608686351</v>
+        <v>0.0037092938486615</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.252163215825388</v>
+        <v>0.0091573191888832</v>
       </c>
       <c r="AH62" t="n">
-        <v>9.992007221626409e-16</v>
+        <v>0.931174569989936</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.11096317330824e-14</v>
+        <v>0.937762133497109</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ARAP1</t>
+          <t>GCKR</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6980,91 +6756,109 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-2.1893</v>
+        <v>7.2518</v>
       </c>
       <c r="D63" t="n">
-        <v>0.0285764313249237</v>
+        <v>4.113964062868456e-13</v>
       </c>
       <c r="E63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>-2.2401</v>
+        <v>9.5787</v>
       </c>
       <c r="G63" t="n">
-        <v>0.0250820660098416</v>
+        <v>9.826532532795896e-22</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0072</v>
+        <v>-3.9335</v>
       </c>
       <c r="J63" t="n">
-        <v>0.3138422736412377</v>
+        <v>8.372721722947615e-05</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>7.2518</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4.113964062868489e-13</v>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>9.5787</v>
+      </c>
+      <c r="P63" t="n">
+        <v>9.826532532795896e-22</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>1</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-3.9335</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8.372721722947569e-05</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
       <c r="U63" t="n">
-        <v>-2.1893</v>
+        <v>10.2386</v>
       </c>
       <c r="V63" t="n">
-        <v>0.0285750423661574</v>
+        <v>1.331127213078415e-24</v>
       </c>
       <c r="W63" t="n">
-        <v>0.0550592279738154</v>
+        <v>1.502272140474211e-23</v>
       </c>
       <c r="X63" t="n">
-        <v>-2.2401</v>
+        <v>13.5239</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.0250844315458308</v>
+        <v>1.129976673358257e-41</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.0535586511383956</v>
+        <v>1.785363143906045e-40</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.0072</v>
+        <v>-5.5536</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.3138386730839759</v>
+        <v>2.798364982571364e-08</v>
       </c>
       <c r="AC63" t="n">
-        <v>0.4657660339270856</v>
+        <v>1.228171297906321e-07</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.0285764313249237</v>
+        <v>4.11448652926083e-13</v>
       </c>
       <c r="AE63" t="n">
-        <v>0.0532156006338468</v>
+        <v>2.70870363176338e-12</v>
       </c>
       <c r="AF63" t="n">
-        <v>0.0250820660098415</v>
+        <v>9.992007221626409e-16</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.0508072619173714</v>
+        <v>1.3887039666353e-14</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.3138422736412377</v>
+        <v>8.372721722949006e-05</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.4231984237887758</v>
+        <v>0.0002544019292742</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CAMK1D</t>
+          <t>GRB14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7073,109 +6867,109 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3.6323</v>
+        <v>-0.618</v>
       </c>
       <c r="D64" t="n">
-        <v>0.0002808956445578</v>
+        <v>0.5365742435188872</v>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>1.8158</v>
+        <v>-0.9399</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0694002600206037</v>
+        <v>0.3472703081026264</v>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>1.9132</v>
+        <v>1.5633</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0557198680582857</v>
+        <v>0.1179746153342791</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>3.9862</v>
+        <v>3.2408</v>
       </c>
       <c r="M64" t="n">
-        <v>6.712664830009929e-05</v>
+        <v>0.0011917861428151</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>2.8468</v>
+        <v>7.0874</v>
       </c>
       <c r="P64" t="n">
-        <v>0.0044154647442019</v>
+        <v>1.366889798371779e-12</v>
       </c>
       <c r="Q64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>-2.2566</v>
+        <v>-6.2231</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0240354968781957</v>
+        <v>4.873806212658002e-10</v>
       </c>
       <c r="T64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>5.3926</v>
+        <v>2.0084</v>
       </c>
       <c r="V64" t="n">
-        <v>6.945732676918269e-08</v>
+        <v>0.0445983207207531</v>
       </c>
       <c r="W64" t="n">
-        <v>3.227722832214961e-07</v>
+        <v>0.0782948297097666</v>
       </c>
       <c r="X64" t="n">
-        <v>3.3334</v>
+        <v>4.6661</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.0008578532228143</v>
+        <v>3.069358483068155e-06</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.0026065540231666</v>
+        <v>1.154663429344687e-05</v>
       </c>
       <c r="AA64" t="n">
-        <v>-0.412</v>
+        <v>-3.6061</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.6803720208725349</v>
+        <v>0.0003108259614143</v>
       </c>
       <c r="AC64" t="n">
-        <v>0.7465193006795869</v>
+        <v>0.000876973248276</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.0001046560677132</v>
+        <v>0.002254608106923</v>
       </c>
       <c r="AE64" t="n">
-        <v>0.0003062159018275</v>
+        <v>0.0050889725841977</v>
       </c>
       <c r="AF64" t="n">
-        <v>0.007907617288291501</v>
+        <v>2.584987779385983e-12</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.0178486218792867</v>
+        <v>1.361426897143284e-11</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.0328546405277713</v>
+        <v>9.216775120890475e-10</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.0639912094596449</v>
+        <v>3.640626172751736e-09</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CDKAL1</t>
+          <t>HHEX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7184,109 +6978,109 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-2.0927</v>
+        <v>2.0459</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0363775144756356</v>
+        <v>0.0407669174045843</v>
       </c>
       <c r="E65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>-1.5653</v>
+        <v>1.1674</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1175049670460892</v>
+        <v>0.2430314489076028</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.5143</v>
+        <v>2.8637</v>
       </c>
       <c r="J65" t="n">
-        <v>0.1299446868966723</v>
+        <v>0.0041870375191572</v>
       </c>
       <c r="K65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>6.6261</v>
+        <v>2.0459</v>
       </c>
       <c r="M65" t="n">
-        <v>3.446535018940334e-11</v>
+        <v>0.0407680641825478</v>
       </c>
       <c r="N65" t="n">
         <v>2</v>
       </c>
       <c r="O65" t="n">
-        <v>9.1975</v>
+        <v>1.1705</v>
       </c>
       <c r="P65" t="n">
-        <v>3.663173202964827e-20</v>
+        <v>0.2417825620228859</v>
       </c>
       <c r="Q65" t="n">
         <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>0.9555</v>
+        <v>2.8636</v>
       </c>
       <c r="S65" t="n">
-        <v>0.3392996943147763</v>
+        <v>0.0041885713574811</v>
       </c>
       <c r="T65" t="n">
         <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>3.5548</v>
+        <v>2.8886</v>
       </c>
       <c r="V65" t="n">
-        <v>0.000378287505112</v>
+        <v>0.0038701928667516</v>
       </c>
       <c r="W65" t="n">
-        <v>0.0009961570967951</v>
+        <v>0.008992506955099301</v>
       </c>
       <c r="X65" t="n">
-        <v>5.8254</v>
+        <v>1.6505</v>
       </c>
       <c r="Y65" t="n">
-        <v>5.69594973925359e-09</v>
+        <v>0.0988333732534132</v>
       </c>
       <c r="Z65" t="n">
-        <v>2.368315944215966e-08</v>
+        <v>0.1730383312804207</v>
       </c>
       <c r="AA65" t="n">
-        <v>-0.2941</v>
+        <v>4.0431</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.7687122242793872</v>
+        <v>5.274723271567715e-05</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.813140941086305</v>
+        <v>0.0001736263076891</v>
       </c>
       <c r="AD65" t="n">
-        <v>6.517697492824935e-11</v>
+        <v>0.0407675238097644</v>
       </c>
       <c r="AE65" t="n">
-        <v>3.4326540128878e-10</v>
+        <v>0.0670965496035706</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.887379141862766e-15</v>
+        <v>0.2423697602866308</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.3887039666353e-14</v>
+        <v>0.330124328666273</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.1994242852337244</v>
+        <v>0.0041878484688581</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.3029715102589275</v>
+        <v>0.0106267855656067</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DUSP8</t>
+          <t>JAZF1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7295,109 +7089,109 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2.0892</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0366929545235972</v>
+        <v>0.9480474444473064</v>
       </c>
       <c r="E66" t="n">
         <v>2</v>
       </c>
       <c r="F66" t="n">
-        <v>-1.1506</v>
+        <v>2.0074</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2498869481516166</v>
+        <v>0.0447115471430717</v>
       </c>
       <c r="H66" t="n">
         <v>2</v>
       </c>
       <c r="I66" t="n">
-        <v>1.4254</v>
+        <v>0.2166</v>
       </c>
       <c r="J66" t="n">
-        <v>0.1540309916336558</v>
+        <v>0.8285253094749793</v>
       </c>
       <c r="K66" t="n">
         <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>6.2101</v>
+        <v>-2.429</v>
       </c>
       <c r="M66" t="n">
-        <v>5.296314080169554e-10</v>
+        <v>0.0151419342731214</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O66" t="n">
-        <v>-3.8558</v>
+        <v>-1.4627</v>
       </c>
       <c r="P66" t="n">
-        <v>0.0001153738035338</v>
+        <v>0.1435524004369689</v>
       </c>
       <c r="Q66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>2.897</v>
+        <v>-0.8571</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0037671075975908</v>
+        <v>0.3913985011846761</v>
       </c>
       <c r="T66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U66" t="n">
-        <v>3.2465</v>
+        <v>-1.7701</v>
       </c>
       <c r="V66" t="n">
-        <v>0.0011682095779781</v>
+        <v>0.0767099064476611</v>
       </c>
       <c r="W66" t="n">
-        <v>0.0027966229290992</v>
+        <v>0.1262517210284423</v>
       </c>
       <c r="X66" t="n">
-        <v>-3.6442</v>
+        <v>0.2434</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.0002682339595988</v>
+        <v>0.80766795615233</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.0008476193123323</v>
+        <v>0.8622401153518118</v>
       </c>
       <c r="AA66" t="n">
-        <v>3.1112</v>
+        <v>-0.4958</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.0018634488452516</v>
+        <v>0.6200303362379317</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.0046003893367149</v>
+        <v>0.7098898052579218</v>
       </c>
       <c r="AD66" t="n">
-        <v>1.001577210058002e-09</v>
+        <v>0.0384117925071439</v>
       </c>
       <c r="AE66" t="n">
-        <v>4.945287474661386e-09</v>
+        <v>0.0646912572863728</v>
       </c>
       <c r="AF66" t="n">
-        <v>0.0002181109791081</v>
+        <v>0.0707547281651912</v>
       </c>
       <c r="AG66" t="n">
-        <v>0.0006153845481979</v>
+        <v>0.1215135548923936</v>
       </c>
       <c r="AH66" t="n">
-        <v>0.0069829855726626</v>
+        <v>0.6721711858265097</v>
       </c>
       <c r="AI66" t="n">
-        <v>0.0162251723600102</v>
+        <v>0.7352209558357913</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FTO</t>
+          <t>KCNJ11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7406,109 +7200,109 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-0.0621</v>
+        <v>0.1812</v>
       </c>
       <c r="D67" t="n">
-        <v>0.9504993091358028</v>
+        <v>0.8561959377418524</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" t="n">
-        <v>4.7555</v>
+        <v>0.351</v>
       </c>
       <c r="G67" t="n">
-        <v>1.979164533662419e-06</v>
+        <v>0.725592970385819</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I67" t="n">
-        <v>-12.8992</v>
+        <v>-0.0405</v>
       </c>
       <c r="J67" t="n">
-        <v>4.547462963785542e-38</v>
+        <v>0.9677029088631972</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L67" t="n">
-        <v>9.3398</v>
+        <v>1.6434</v>
       </c>
       <c r="M67" t="n">
-        <v>9.65465651174031e-21</v>
+        <v>0.1003097813529664</v>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>19.6962</v>
+        <v>0.2828</v>
       </c>
       <c r="P67" t="n">
-        <v>2.326425266493951e-86</v>
+        <v>0.7773391356497142</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>-2.0606</v>
+        <v>0.7245</v>
       </c>
       <c r="S67" t="n">
-        <v>0.0393430825266283</v>
+        <v>0.4687834751981203</v>
       </c>
       <c r="T67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>6.9317</v>
+        <v>1.3475</v>
       </c>
       <c r="V67" t="n">
-        <v>4.157083090136175e-12</v>
+        <v>0.1778182979575868</v>
       </c>
       <c r="W67" t="n">
-        <v>2.756858168127347e-11</v>
+        <v>0.2508508131901671</v>
       </c>
       <c r="X67" t="n">
-        <v>17.8688</v>
+        <v>0.4446</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.063120156296528e-71</v>
+        <v>0.6565727702119338</v>
       </c>
       <c r="Z67" t="n">
-        <v>4.074662308685641e-70</v>
+        <v>0.7409892692391825</v>
       </c>
       <c r="AA67" t="n">
-        <v>-10.12</v>
+        <v>0.514</v>
       </c>
       <c r="AB67" t="n">
-        <v>4.504328349173042e-24</v>
+        <v>0.6072768771250887</v>
       </c>
       <c r="AC67" t="n">
-        <v>5.083456279781005e-23</v>
+        <v>0.7098898052579218</v>
       </c>
       <c r="AD67" t="n">
-        <v>1.887379141862766e-15</v>
+        <v>0.3163024051705033</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.66644475996236e-14</v>
+        <v>0.3966331747376152</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.887379141862766e-15</v>
+        <v>0.7550741360845361</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.3887039666353e-14</v>
+        <v>0.8060926587929507</v>
       </c>
       <c r="AH67" t="n">
-        <v>2.109423746787797e-15</v>
+        <v>0.9315166290929332</v>
       </c>
       <c r="AI67" t="n">
-        <v>1.11096317330824e-14</v>
+        <v>0.937762133497109</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCK</t>
+          <t>KLF14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7516,92 +7310,83 @@
           <t>T2DM_Control</t>
         </is>
       </c>
-      <c r="C68" t="n">
-        <v>2.3971</v>
-      </c>
-      <c r="D68" t="n">
-        <v>0.0165264569403382</v>
-      </c>
-      <c r="E68" t="n">
-        <v>3</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-2.9019</v>
-      </c>
-      <c r="G68" t="n">
-        <v>0.0037092938486616</v>
-      </c>
-      <c r="H68" t="n">
-        <v>3</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.0864</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.931174569989936</v>
-      </c>
-      <c r="K68" t="n">
-        <v>3</v>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
+      <c r="L68" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.1505782136990521</v>
+      </c>
+      <c r="N68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.6001087849294473</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>-0.5335</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0.5936670043968274</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
       <c r="U68" t="n">
-        <v>2.3971</v>
+        <v>1.4375</v>
       </c>
       <c r="V68" t="n">
-        <v>0.0165254130035821</v>
+        <v>0.1505759728248468</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0352839899265673</v>
+        <v>0.216281851875689</v>
       </c>
       <c r="X68" t="n">
-        <v>-2.9019</v>
+        <v>0.5242</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.0037090691938899</v>
+        <v>0.600139440905249</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.0097672155439103</v>
+        <v>0.6919679749451318</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.0864</v>
+        <v>-0.5335</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.9311484469318309</v>
+        <v>0.5936875110370833</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.9430862475335208</v>
+        <v>0.7098898052579218</v>
       </c>
       <c r="AD68" t="n">
-        <v>0.0165264569403382</v>
+        <v>0.1505782136990521</v>
       </c>
       <c r="AE68" t="n">
-        <v>0.0326397524571679</v>
+        <v>0.2124228371825914</v>
       </c>
       <c r="AF68" t="n">
-        <v>0.0037092938486615</v>
+        <v>0.6001087849294473</v>
       </c>
       <c r="AG68" t="n">
-        <v>0.0091573191888832</v>
+        <v>0.6677266761891034</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.931174569989936</v>
+        <v>0.5936670043968274</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.937762133497109</v>
+        <v>0.6797057006862227</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GCKR</t>
+          <t>PAM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7609,110 +7394,83 @@
           <t>T2DM_Control</t>
         </is>
       </c>
-      <c r="C69" t="n">
-        <v>7.2518</v>
-      </c>
-      <c r="D69" t="n">
-        <v>4.113964062868456e-13</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v>9.5787</v>
-      </c>
-      <c r="G69" t="n">
-        <v>9.826532532795896e-22</v>
-      </c>
-      <c r="H69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-3.9335</v>
-      </c>
-      <c r="J69" t="n">
-        <v>8.372721722947615e-05</v>
-      </c>
-      <c r="K69" t="n">
-        <v>1</v>
-      </c>
       <c r="L69" t="n">
-        <v>7.2518</v>
+        <v>0.206</v>
       </c>
       <c r="M69" t="n">
-        <v>4.113964062868489e-13</v>
+        <v>0.836781487026655</v>
       </c>
       <c r="N69" t="n">
         <v>1</v>
       </c>
       <c r="O69" t="n">
-        <v>9.5787</v>
+        <v>-0.5945</v>
       </c>
       <c r="P69" t="n">
-        <v>9.826532532795896e-22</v>
+        <v>0.5521663994570822</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>-3.9335</v>
+        <v>-1.4359</v>
       </c>
       <c r="S69" t="n">
-        <v>8.372721722947569e-05</v>
+        <v>0.1510172459998212</v>
       </c>
       <c r="T69" t="n">
         <v>1</v>
       </c>
       <c r="U69" t="n">
-        <v>10.2386</v>
+        <v>0.206</v>
       </c>
       <c r="V69" t="n">
-        <v>1.331127213078415e-24</v>
+        <v>0.8367909113052145</v>
       </c>
       <c r="W69" t="n">
-        <v>1.502272140474211e-23</v>
+        <v>0.8933308377447561</v>
       </c>
       <c r="X69" t="n">
-        <v>13.5239</v>
+        <v>-0.5945</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.129976673358257e-41</v>
+        <v>0.5521777422910252</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.785363143906045e-40</v>
+        <v>0.6510752483729999</v>
       </c>
       <c r="AA69" t="n">
-        <v>-5.5536</v>
+        <v>-1.4359</v>
       </c>
       <c r="AB69" t="n">
-        <v>2.798364982571364e-08</v>
+        <v>0.1510307985045854</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.228171297906321e-07</v>
+        <v>0.2434986343237194</v>
       </c>
       <c r="AD69" t="n">
-        <v>4.11448652926083e-13</v>
+        <v>0.836781487026655</v>
       </c>
       <c r="AE69" t="n">
-        <v>2.70870363176338e-12</v>
+        <v>0.8893247230822036</v>
       </c>
       <c r="AF69" t="n">
-        <v>9.992007221626409e-16</v>
+        <v>0.5521663994570822</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.3887039666353e-14</v>
+        <v>0.6231592222444213</v>
       </c>
       <c r="AH69" t="n">
-        <v>8.372721722949006e-05</v>
+        <v>0.1510172459998212</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.0002544019292742</v>
+        <v>0.2434767843670586</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GRB14</t>
+          <t>PPARG</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7721,109 +7479,109 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-0.618</v>
+        <v>-1.0519</v>
       </c>
       <c r="D70" t="n">
-        <v>0.5365742435188872</v>
+        <v>0.2928588196493487</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9399</v>
+        <v>-2.1678</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3472703081026264</v>
+        <v>0.0301705272096899</v>
       </c>
       <c r="H70" t="n">
         <v>1</v>
       </c>
       <c r="I70" t="n">
-        <v>1.5633</v>
+        <v>-1.1876</v>
       </c>
       <c r="J70" t="n">
-        <v>0.1179746153342791</v>
+        <v>0.2349971788393356</v>
       </c>
       <c r="K70" t="n">
         <v>1</v>
       </c>
       <c r="L70" t="n">
-        <v>3.2408</v>
+        <v>-5.3308</v>
       </c>
       <c r="M70" t="n">
-        <v>0.0011917861428151</v>
+        <v>9.77666210661084e-08</v>
       </c>
       <c r="N70" t="n">
         <v>1</v>
       </c>
       <c r="O70" t="n">
-        <v>7.0874</v>
+        <v>0.2355</v>
       </c>
       <c r="P70" t="n">
-        <v>1.366889798371779e-12</v>
+        <v>0.8138560739572558</v>
       </c>
       <c r="Q70" t="n">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>-6.2231</v>
+        <v>-6.3268</v>
       </c>
       <c r="S70" t="n">
-        <v>4.873806212658002e-10</v>
+        <v>2.502871272746757e-10</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
       </c>
       <c r="U70" t="n">
-        <v>2.0084</v>
+        <v>-4.6798</v>
       </c>
       <c r="V70" t="n">
-        <v>0.0445983207207531</v>
+        <v>2.872164440577701e-06</v>
       </c>
       <c r="W70" t="n">
-        <v>0.0782948297097666</v>
+        <v>1.080480908598278e-05</v>
       </c>
       <c r="X70" t="n">
-        <v>4.6661</v>
+        <v>-1.2664</v>
       </c>
       <c r="Y70" t="n">
-        <v>3.069358483068155e-06</v>
+        <v>0.2053814031599182</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.154663429344687e-05</v>
+        <v>0.3061345443327083</v>
       </c>
       <c r="AA70" t="n">
-        <v>-3.6061</v>
+        <v>-5.5136</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.0003108259614143</v>
+        <v>3.514809087635242e-08</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.000876973248276</v>
+        <v>1.461420620648338e-07</v>
       </c>
       <c r="AD70" t="n">
-        <v>0.002254608106923</v>
+        <v>1.848848080188148e-07</v>
       </c>
       <c r="AE70" t="n">
-        <v>0.0050889725841977</v>
+        <v>7.687315701834931e-07</v>
       </c>
       <c r="AF70" t="n">
-        <v>2.584987779385983e-12</v>
+        <v>0.0751318218478913</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.361426897143284e-11</v>
+        <v>0.1262854026804982</v>
       </c>
       <c r="AH70" t="n">
-        <v>9.216775120890475e-10</v>
+        <v>4.733138325718753e-10</v>
       </c>
       <c r="AI70" t="n">
-        <v>3.640626172751736e-09</v>
+        <v>2.024712149401908e-09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HHEX</t>
+          <t>PROX1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7832,109 +7590,82 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.0459</v>
+        <v>-1.738</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0407669174045843</v>
+        <v>0.0822126809033166</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1.1674</v>
+        <v>-1.6477</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2430314489076028</v>
+        <v>0.0994063680329477</v>
       </c>
       <c r="H71" t="n">
         <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>2.8637</v>
+        <v>-1.8998</v>
       </c>
       <c r="J71" t="n">
-        <v>0.0041870375191572</v>
+        <v>0.0574592710947977</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
       </c>
-      <c r="L71" t="n">
-        <v>2.0459</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.0407680641825478</v>
-      </c>
-      <c r="N71" t="n">
-        <v>2</v>
-      </c>
-      <c r="O71" t="n">
-        <v>1.1705</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0.2417825620228859</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>2</v>
-      </c>
-      <c r="R71" t="n">
-        <v>2.8636</v>
-      </c>
-      <c r="S71" t="n">
-        <v>0.0041885713574811</v>
-      </c>
-      <c r="T71" t="n">
-        <v>2</v>
-      </c>
       <c r="U71" t="n">
-        <v>2.8886</v>
+        <v>-1.738</v>
       </c>
       <c r="V71" t="n">
-        <v>0.0038701928667516</v>
+        <v>0.08221081377542259</v>
       </c>
       <c r="W71" t="n">
-        <v>0.008992506955099301</v>
+        <v>0.1325439650664977</v>
       </c>
       <c r="X71" t="n">
-        <v>1.6505</v>
+        <v>-1.6477</v>
       </c>
       <c r="Y71" t="n">
-        <v>0.0988333732534132</v>
+        <v>0.0994142480539857</v>
       </c>
       <c r="Z71" t="n">
         <v>0.1730383312804207</v>
       </c>
       <c r="AA71" t="n">
-        <v>4.0431</v>
+        <v>-1.8998</v>
       </c>
       <c r="AB71" t="n">
-        <v>5.274723271567715e-05</v>
+        <v>0.0574593709451721</v>
       </c>
       <c r="AC71" t="n">
-        <v>0.0001736263076891</v>
+        <v>0.1030026393709981</v>
       </c>
       <c r="AD71" t="n">
-        <v>0.0407675238097644</v>
+        <v>0.0822126809033165</v>
       </c>
       <c r="AE71" t="n">
-        <v>0.0670965496035706</v>
+        <v>0.1298960358272401</v>
       </c>
       <c r="AF71" t="n">
-        <v>0.2423697602866308</v>
+        <v>0.0994063680329476</v>
       </c>
       <c r="AG71" t="n">
-        <v>0.330124328666273</v>
+        <v>0.1539824132275071</v>
       </c>
       <c r="AH71" t="n">
-        <v>0.0041878484688581</v>
+        <v>0.0574592710947977</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.0106267855656067</v>
+        <v>0.0986800525323699</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>JAZF1</t>
+          <t>RREB1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7943,109 +7674,82 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.06519999999999999</v>
+        <v>3.8128</v>
       </c>
       <c r="D72" t="n">
-        <v>0.9480474444473064</v>
+        <v>0.0001373880739983</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>2.0074</v>
+        <v>0.7457</v>
       </c>
       <c r="G72" t="n">
-        <v>0.0447115471430717</v>
+        <v>0.4558221958768151</v>
       </c>
       <c r="H72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2166</v>
+        <v>1.9316</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8285253094749793</v>
+        <v>0.0534032748723322</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" t="n">
-        <v>-2.429</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0.0151419342731214</v>
-      </c>
-      <c r="N72" t="n">
-        <v>3</v>
-      </c>
-      <c r="O72" t="n">
-        <v>-1.4627</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0.1435524004369689</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>3</v>
-      </c>
-      <c r="R72" t="n">
-        <v>-0.8571</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0.3913985011846761</v>
-      </c>
-      <c r="T72" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U72" t="n">
-        <v>-1.7701</v>
+        <v>3.8128</v>
       </c>
       <c r="V72" t="n">
-        <v>0.0767099064476611</v>
+        <v>0.0001374012956414</v>
       </c>
       <c r="W72" t="n">
-        <v>0.1262517210284423</v>
+        <v>0.000387667941274</v>
       </c>
       <c r="X72" t="n">
-        <v>0.2434</v>
+        <v>0.7457</v>
       </c>
       <c r="Y72" t="n">
-        <v>0.80766795615233</v>
+        <v>0.455848659186304</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.8622401153518118</v>
+        <v>0.5716197472336193</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.4958</v>
+        <v>1.9316</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.6200303362379317</v>
+        <v>0.0534088958593993</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.7098898052579218</v>
+        <v>0.09812332029982671</v>
       </c>
       <c r="AD72" t="n">
-        <v>0.0384117925071439</v>
+        <v>0.0001373880739983</v>
       </c>
       <c r="AE72" t="n">
-        <v>0.0646912572863728</v>
+        <v>0.0003876306373524</v>
       </c>
       <c r="AF72" t="n">
-        <v>0.0707547281651912</v>
+        <v>0.4558221958768151</v>
       </c>
       <c r="AG72" t="n">
-        <v>0.1215135548923936</v>
+        <v>0.5539992842195137</v>
       </c>
       <c r="AH72" t="n">
-        <v>0.6721711858265097</v>
+        <v>0.0534032748723322</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.7352209558357913</v>
+        <v>0.0937524158869833</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>KCNJ11</t>
+          <t>SLC16A11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8054,109 +7758,82 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.1812</v>
+        <v>-5.0709</v>
       </c>
       <c r="D73" t="n">
-        <v>0.8561959377418524</v>
+        <v>3.958978025514228e-07</v>
       </c>
       <c r="E73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>0.351</v>
+        <v>-5.4875</v>
       </c>
       <c r="G73" t="n">
-        <v>0.725592970385819</v>
+        <v>4.076085521337968e-08</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0405</v>
+        <v>11.8045</v>
       </c>
       <c r="J73" t="n">
-        <v>0.9677029088631972</v>
+        <v>3.699025700172539e-32</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" t="n">
-        <v>1.6434</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0.1003097813529664</v>
-      </c>
-      <c r="N73" t="n">
-        <v>1</v>
-      </c>
-      <c r="O73" t="n">
-        <v>0.2828</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0.7773391356497142</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="n">
-        <v>0.7245</v>
-      </c>
-      <c r="S73" t="n">
-        <v>0.4687834751981203</v>
-      </c>
-      <c r="T73" t="n">
         <v>1</v>
       </c>
       <c r="U73" t="n">
-        <v>1.3475</v>
+        <v>-5.0709</v>
       </c>
       <c r="V73" t="n">
-        <v>0.1778182979575868</v>
+        <v>3.959387901151274e-07</v>
       </c>
       <c r="W73" t="n">
-        <v>0.2508508131901671</v>
+        <v>1.737731356616393e-06</v>
       </c>
       <c r="X73" t="n">
-        <v>0.4446</v>
+        <v>-5.4875</v>
       </c>
       <c r="Y73" t="n">
-        <v>0.6565727702119338</v>
+        <v>4.07662016965699e-08</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.7409892692391825</v>
+        <v>1.610264967014511e-07</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.514</v>
+        <v>11.8045</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.6072768771250887</v>
+        <v>3.699836856629588e-32</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.7098898052579218</v>
+        <v>7.307177791843435e-31</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.3163024051705033</v>
+        <v>3.95897802540901e-07</v>
       </c>
       <c r="AE73" t="n">
-        <v>0.3966331747376152</v>
+        <v>1.563796320036559e-06</v>
       </c>
       <c r="AF73" t="n">
-        <v>0.7550741360845361</v>
+        <v>4.076085519111317e-08</v>
       </c>
       <c r="AG73" t="n">
-        <v>0.8060926587929507</v>
+        <v>1.400046765259974e-07</v>
       </c>
       <c r="AH73" t="n">
-        <v>0.9315166290929332</v>
+        <v>9.992007221626409e-16</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.937762133497109</v>
+        <v>1.11096317330824e-14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>KLF14</t>
+          <t>ST6GAL1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8164,680 +7841,219 @@
           <t>T2DM_Control</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="C74" t="n">
+        <v>1.6809</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0927843701523476</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6844</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.4937110991108813</v>
+      </c>
+      <c r="H74" t="n">
+        <v>2</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1.2191</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.2228054920378465</v>
+      </c>
+      <c r="K74" t="n">
+        <v>2</v>
+      </c>
       <c r="L74" t="n">
-        <v>1.4375</v>
+        <v>-0.8062</v>
       </c>
       <c r="M74" t="n">
-        <v>0.1505782136990521</v>
+        <v>0.4201147395642534</v>
       </c>
       <c r="N74" t="n">
         <v>1</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5242</v>
+        <v>-2.8081</v>
       </c>
       <c r="P74" t="n">
-        <v>0.6001087849294473</v>
+        <v>0.0049827763457749</v>
       </c>
       <c r="Q74" t="n">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>-0.5335</v>
+        <v>-2.4228</v>
       </c>
       <c r="S74" t="n">
-        <v>0.5936670043968274</v>
+        <v>0.0154026324559752</v>
       </c>
       <c r="T74" t="n">
         <v>1</v>
       </c>
       <c r="U74" t="n">
-        <v>1.4375</v>
+        <v>0.5164</v>
       </c>
       <c r="V74" t="n">
-        <v>0.1505759728248468</v>
+        <v>0.6056017000731595</v>
       </c>
       <c r="W74" t="n">
-        <v>0.216281851875689</v>
+        <v>0.6738385113490085</v>
       </c>
       <c r="X74" t="n">
-        <v>0.5242</v>
+        <v>-1.6412</v>
       </c>
       <c r="Y74" t="n">
-        <v>0.600139440905249</v>
+        <v>0.1007564966949285</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.6919679749451318</v>
+        <v>0.1730383312804207</v>
       </c>
       <c r="AA74" t="n">
-        <v>-0.5335</v>
+        <v>-0.9978</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.5936875110370833</v>
+        <v>0.3183717193931977</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.7098898052579218</v>
+        <v>0.4657660339270856</v>
       </c>
       <c r="AD74" t="n">
-        <v>0.1505782136990521</v>
+        <v>0.1687592014401647</v>
       </c>
       <c r="AE74" t="n">
-        <v>0.2124228371825914</v>
+        <v>0.2338943318205792</v>
       </c>
       <c r="AF74" t="n">
-        <v>0.6001087849294473</v>
+        <v>0.009418269673860899</v>
       </c>
       <c r="AG74" t="n">
-        <v>0.6677266761891034</v>
+        <v>0.0201092784928382</v>
       </c>
       <c r="AH74" t="n">
-        <v>0.5936670043968274</v>
+        <v>0.0276598390546199</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.6797057006862227</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>PAM</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0.836781487026655</v>
-      </c>
-      <c r="N75" t="n">
-        <v>1</v>
-      </c>
-      <c r="O75" t="n">
-        <v>-0.5945</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0.5521663994570822</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>1</v>
-      </c>
-      <c r="R75" t="n">
-        <v>-1.4359</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0.1510172459998212</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="V75" t="n">
-        <v>0.8367909113052145</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0.8933308377447561</v>
-      </c>
-      <c r="X75" t="n">
-        <v>-0.5945</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0.5521777422910252</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>0.6510752483729999</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>-1.4359</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>0.1510307985045854</v>
-      </c>
-      <c r="AC75" t="n">
-        <v>0.2434986343237194</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>0.836781487026655</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>0.8893247230822036</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>0.5521663994570822</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>0.6231592222444213</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>0.1510172459998212</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>0.2434767843670586</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>PPARG</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.0519</v>
-      </c>
-      <c r="D76" t="n">
-        <v>0.2928588196493487</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
-      <c r="F76" t="n">
-        <v>-2.1678</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.0301705272096899</v>
-      </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="n">
-        <v>-1.1876</v>
-      </c>
-      <c r="J76" t="n">
-        <v>0.2349971788393356</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>-5.3308</v>
-      </c>
-      <c r="M76" t="n">
-        <v>9.77666210661084e-08</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0.2355</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0.8138560739572558</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>1</v>
-      </c>
-      <c r="R76" t="n">
-        <v>-6.3268</v>
-      </c>
-      <c r="S76" t="n">
-        <v>2.502871272746757e-10</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1</v>
-      </c>
-      <c r="U76" t="n">
-        <v>-4.6798</v>
-      </c>
-      <c r="V76" t="n">
-        <v>2.872164440577701e-06</v>
-      </c>
-      <c r="W76" t="n">
-        <v>1.080480908598278e-05</v>
-      </c>
-      <c r="X76" t="n">
-        <v>-1.2664</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0.2053814031599182</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>0.3061345443327083</v>
-      </c>
-      <c r="AA76" t="n">
-        <v>-5.5136</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>3.514809087635242e-08</v>
-      </c>
-      <c r="AC76" t="n">
-        <v>1.461420620648338e-07</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1.848848080188148e-07</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>7.687315701834931e-07</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>0.0751318218478913</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>0.1262854026804982</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>4.733138325718753e-10</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>2.024712149401908e-09</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>PROX1</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.738</v>
-      </c>
-      <c r="D77" t="n">
-        <v>0.0822126809033166</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>-1.6477</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0.0994063680329477</v>
-      </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="n">
-        <v>-1.8998</v>
-      </c>
-      <c r="J77" t="n">
-        <v>0.0574592710947977</v>
-      </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="n">
-        <v>-1.738</v>
-      </c>
-      <c r="V77" t="n">
-        <v>0.08221081377542259</v>
-      </c>
-      <c r="W77" t="n">
-        <v>0.1325439650664977</v>
-      </c>
-      <c r="X77" t="n">
-        <v>-1.6477</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>0.0994142480539857</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>0.1730383312804207</v>
-      </c>
-      <c r="AA77" t="n">
-        <v>-1.8998</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>0.0574593709451721</v>
-      </c>
-      <c r="AC77" t="n">
-        <v>0.1030026393709981</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>0.0822126809033165</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>0.1298960358272401</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>0.0994063680329476</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>0.1539824132275071</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>0.0574592710947977</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>0.0986800525323699</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>RREB1</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>3.8128</v>
-      </c>
-      <c r="D78" t="n">
-        <v>0.0001373880739983</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.7457</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0.4558221958768151</v>
-      </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
-      <c r="I78" t="n">
-        <v>1.9316</v>
-      </c>
-      <c r="J78" t="n">
-        <v>0.0534032748723322</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="n">
-        <v>3.8128</v>
-      </c>
-      <c r="V78" t="n">
-        <v>0.0001374012956414</v>
-      </c>
-      <c r="W78" t="n">
-        <v>0.000387667941274</v>
-      </c>
-      <c r="X78" t="n">
-        <v>0.7457</v>
-      </c>
-      <c r="Y78" t="n">
-        <v>0.455848659186304</v>
-      </c>
-      <c r="Z78" t="n">
-        <v>0.5716197472336193</v>
-      </c>
-      <c r="AA78" t="n">
-        <v>1.9316</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>0.0534088958593993</v>
-      </c>
-      <c r="AC78" t="n">
-        <v>0.09812332029982671</v>
-      </c>
-      <c r="AD78" t="n">
-        <v>0.0001373880739983</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>0.0003876306373524</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>0.4558221958768151</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>0.5539992842195137</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>0.0534032748723322</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>0.0937524158869833</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SLC16A11</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>-5.0709</v>
-      </c>
-      <c r="D79" t="n">
-        <v>3.958978025514228e-07</v>
-      </c>
-      <c r="E79" t="n">
-        <v>1</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-5.4875</v>
-      </c>
-      <c r="G79" t="n">
-        <v>4.076085521337968e-08</v>
-      </c>
-      <c r="H79" t="n">
-        <v>1</v>
-      </c>
-      <c r="I79" t="n">
-        <v>11.8045</v>
-      </c>
-      <c r="J79" t="n">
-        <v>3.699025700172539e-32</v>
-      </c>
-      <c r="K79" t="n">
-        <v>1</v>
-      </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="n">
-        <v>-5.0709</v>
-      </c>
-      <c r="V79" t="n">
-        <v>3.959387901151274e-07</v>
-      </c>
-      <c r="W79" t="n">
-        <v>1.737731356616393e-06</v>
-      </c>
-      <c r="X79" t="n">
-        <v>-5.4875</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>4.07662016965699e-08</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>1.610264967014511e-07</v>
-      </c>
-      <c r="AA79" t="n">
-        <v>11.8045</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>3.699836856629588e-32</v>
-      </c>
-      <c r="AC79" t="n">
-        <v>7.307177791843435e-31</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>3.95897802540901e-07</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>1.563796320036559e-06</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>4.076085519111317e-08</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>1.400046765259974e-07</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>9.992007221626409e-16</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>1.11096317330824e-14</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>ST6GAL1</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>T2DM_Control</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>1.6809</v>
-      </c>
-      <c r="D80" t="n">
-        <v>0.0927843701523476</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.6844</v>
-      </c>
-      <c r="G80" t="n">
-        <v>0.4937110991108813</v>
-      </c>
-      <c r="H80" t="n">
-        <v>2</v>
-      </c>
-      <c r="I80" t="n">
-        <v>1.2191</v>
-      </c>
-      <c r="J80" t="n">
-        <v>0.2228054920378465</v>
-      </c>
-      <c r="K80" t="n">
-        <v>2</v>
-      </c>
-      <c r="L80" t="n">
-        <v>-0.8062</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0.4201147395642534</v>
-      </c>
-      <c r="N80" t="n">
-        <v>1</v>
-      </c>
-      <c r="O80" t="n">
-        <v>-2.8081</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0.0049827763457749</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>1</v>
-      </c>
-      <c r="R80" t="n">
-        <v>-2.4228</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0.0154026324559752</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0.5164</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0.6056017000731595</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0.6738385113490085</v>
-      </c>
-      <c r="X80" t="n">
-        <v>-1.6412</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>0.1007564966949285</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>0.1730383312804207</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>-0.9978</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>0.3183717193931977</v>
-      </c>
-      <c r="AC80" t="n">
-        <v>0.4657660339270856</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>0.1687592014401647</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>0.2338943318205792</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>0.009418269673860899</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>0.0201092784928382</v>
-      </c>
-      <c r="AH80" t="n">
-        <v>0.0276598390546199</v>
-      </c>
-      <c r="AI80" t="n">
         <v>0.059057494197702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>**Supplementary Table S2.** GTEx v8 baseline TWAS results for all analyzed genes across two tissues (Nerve_Tibial and Whole_Blood) and three diabetic complications (DR, DN, DPN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>- **Gene:** HGNC gene symbol</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>- **Group:** Candidate / NonCandidate / T2DM_Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>- **Z_Nerve_Tibial_{trait}:** S-PrediXcan Z-score using GTEx v8 Nerve_Tibial eQTL weights</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>- **P_Nerve_Tibial_{trait}:** Corresponding P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>- **SNPs_Model_Nerve_Tibial_{trait}:** Number of SNPs in the predictive model for this tissue-trait pair</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- **Z_Whole_Blood_{trait}:** S-PrediXcan Z-score using GTEx v8 Whole_Blood eQTL weights</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>- **P_Whole_Blood_{trait}:** Corresponding P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>- **SNPs_Model_Whole_Blood_{trait}:** Number of SNPs in the predictive model</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>- **Z_Multi_{trait}:** Stouffer's weighted Z-meta multi-tissue integrated Z-score</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>- **P_Multi_{trait}:** Corresponding P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>- **FDR_Multi_{trait}:** Benjamini-Hochberg FDR q-value across multi-tissue integrated results</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>- **P_ACAT_O_{trait}:** Aggregated Cauchy Association Test Omnibus P-value (LD-robust)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>- **FDR_ACAT_O_{trait}:** FDR q-value for ACAT-O results</t>
+        </is>
       </c>
     </row>
   </sheetData>
